--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N82_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N82_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.426708131192341</v>
+        <v>1.044340071318755</v>
       </c>
       <c r="D2" t="n">
-        <v>49.26091825700475</v>
+        <v>8.004899216763272</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
